--- a/platform_core_data/modules/branch/test_design/TestCases_Branch.xlsx
+++ b/platform_core_data/modules/branch/test_design/TestCases_Branch.xlsx
@@ -60,7 +60,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L82"/>
+  <dimension ref="A1:L113"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -178,7 +178,7 @@
       </c>
       <c r="G2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Branch is saved and its status shows "Pending for approval."</t>
+          <t xml:space="preserve">After clicking **Send For Approval**, the Branch is created successfully and the application shows the success message "Added Successfully." The new Branch is then **retrievable under the `Inactive` Status filter**, and **must not** appear under the `Active` Status filter at this stage.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr" s="2">
@@ -189,6 +189,14 @@
       <c r="I2" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Atomic, Positive</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Corrected twice on 2026-08-10 by business instruction (both Stage 3 decisions):
+1. **Success message.** The application's actual post-submit success message is "Added Successfully," not "Pending for approval." — the original expected value asserted a message this screen never shows. "Pending for approval" remains the correct, separate value of the Approval Status *column* in the results grid (TC-BR-053/054), which this correction does not touch.
+2. **Persistence and placement (added).** The expected result now requires the created Branch to be **found under `Inactive`**, and explicitly not under `Active`, at this stage. This is a deliberate strengthening: the prior version asserted only submit-time signals (navigation or toast), which pass even when nothing retrievable was created — the precise reason the "record reports success but is not retrievable" condition went unnoticed by a green TC-BR-001. Verifying placement necessarily also verifies persistence, so this closes that gap rather than needing a separate case.
+**Open verification note:** the automation's provisioning previously searched with Status `Both` and found nothing after a successful submit. Under this clarified rule the correct filter is `Inactive`. Whether `Both` failing to return a newly created Inactive record is itself an application defect has **not** been established — if a follow-up run shows `Inactive` returns the record while `Both` does not, that is a new finding about the `Both` filter, not a test problem, and must be raised rather than absorbed.</t>
         </is>
       </c>
       <c r="K2" t="inlineStr" s="2">
@@ -1714,12 +1722,13 @@
       </c>
       <c r="I27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Atomic, Negative-BoundaryValues, Regression</t>
+          <t xml:space="preserve">Atomic, Negative-BoundaryValues, Regression, Blocked-NeedsClarification
+**Blocking Reason (2026-08-10):** This case's own Test Data is no longer valid business data. It sets Credit Terms(Days) to 15 digits specifically so the cross-field rule is satisfied and cannot mask the length check — but Credit Terms(Days) was confirmed on 2026-08-10 to have a **7-digit maximum**, so a 15-digit value is not legal input. And no legal substitute exists: reaching Warning Prompt's 11-digit boundary needs 12+ digits, which necessarily exceeds the largest legal Credit Terms value (9999999), and Credit Terms is Mandatory so it cannot be left blank to avoid the comparison. **The two documented rules cannot both be satisfied by any valid business data** — see FINDING-016 (`Needs Human Review`). Do not execute, do not automate, and do not substitute a value that makes the case runnable at the cost of its stated intent: the isolation from TC-BR-027's cross-field rule *is* the objective, not an implementation detail of it. **Required to unblock:** a business decision on whether Warning Prompt (Days)'s 11-digit maximum remains a real requirement given Credit Terms' 7-digit cap, and if so, how it is intended to be reachable.</t>
         </is>
       </c>
       <c r="J27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Module-owner-supplied evidence (2026-08-03) confirmed the live application also enforces a separate cross-field rule — "Warning prompt days should not be greater than credit terms days" (see TC-BR-027) — that fires whenever Warning Prompt (Days) &gt; Credit Terms (Days). The original version of this test case entered only Warning Prompt(Days) with Credit Terms(Days) left blank, which the module owner flagged as incorrect: with Credit Terms unset, any resulting message could be the cross-field rule rather than a length-specific one, so the test did not actually isolate FINDING-004's length-cap defect. Test Data now sets Credit Terms(Days) to the same value as Warning Prompt(Days) so the cross-field rule is satisfied (not violated) and cannot mask the length check. Regression test for FINDING-004 — as of Discovery 2026-08-03, a 14-digit value was fully accepted with no truncation or error; this case must fail against that observed behavior and pass only once the max-length rule is enforced.</t>
+          <t xml:space="preserve">Module-owner-supplied evidence (2026-08-03) confirmed the live application also enforces a separate cross-field rule — "Warning prompt days should not be greater than credit terms days" (see TC-BR-027) — that fires whenever Warning Prompt (Days) &gt; Credit Terms (Days). The original version of this test case entered only Warning Prompt(Days) with Credit Terms(Days) left blank, which the module owner flagged as incorrect: with Credit Terms unset, any resulting message could be the cross-field rule rather than a length-specific one, so the test did not actually isolate FINDING-004's length-cap defect. Test Data therefore sets Credit Terms(Days) to the same value as Warning Prompt(Days) so the cross-field rule is satisfied (not violated) and cannot mask the length check — the intent that the 7-digit Credit Terms cap has now made unsatisfiable. Regression test for FINDING-004 — as of Discovery 2026-08-03, a 14-digit value was fully accepted with no truncation or error; this case must fail against that observed behavior and pass only once the max-length rule is enforced.</t>
         </is>
       </c>
       <c r="K27" t="inlineStr" s="2">
@@ -1729,7 +1738,7 @@
       </c>
       <c r="L27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Approved</t>
+          <t xml:space="preserve">Blocked — Needs Clarification (was Approved; suspended 2026-08-10, not rejected on merit)</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1793,7 @@
       </c>
       <c r="J28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Confirmed via module-owner-supplied screenshot (2026-08-03) showing the exact live behavior and message text with these Test Data values — this closes Discovery's OQ-BR-2 and resolves RISK-BR-2 in full (ProjectContext.md §6). No longer assumption-based; Evidence Category is Human Observation (module-owner-provided, not independently reproduced by Explorer this run). The rule is strictly-greater-than — equal values (e.g. both 10000) are not expected to be rejected; that boundary is not separately re-verified here and remains an assumption if a future case needs it.</t>
+          <t xml:space="preserve">Confirmed via module-owner-supplied screenshot (2026-08-03) showing the exact live behavior and message text with these Test Data values — this closes Discovery's OQ-BR-2 and resolves RISK-BR-2 in full (ProjectContext.md §6). No longer assumption-based; Evidence Category is Human Observation (module-owner-provided, not independently reproduced by Explorer this run). The rule is strictly-greater-than — equal values (e.g. both 10000) are not expected to be rejected; that boundary is not separately re-verified here and remains an assumption if a future case needs it. **Added 2026-08-10 (user instruction):** Credit Terms (Days) additionally has its own **7-digit maximum length**, a constraint not stated in PRD_UserStories.md (which documents Credit Terms only as "numeric input only, Mandatory"). That cap interacts with TC-BR-026's 11-digit Warning Prompt case in a way that makes isolation impossible — see FINDING-016 and TC-BR-026 Notes.</t>
         </is>
       </c>
       <c r="K28" t="inlineStr" s="2">
@@ -2360,12 +2369,12 @@
       </c>
       <c r="B39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Child Agencies Threshold Amount blocks submission when empty</t>
+          <t xml:space="preserve">Child Agencies Threshold Amount opens pre-filled with a default value</t>
         </is>
       </c>
       <c r="C39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Verify that the Outstanding Threshold field blocks submission when left empty.</t>
+          <t xml:space="preserve">Verify that the Outstanding Threshold field already carries a value when the Add Branch form first opens.</t>
         </is>
       </c>
       <c r="D39" t="inlineStr" s="2">
@@ -2375,12 +2384,12 @@
       </c>
       <c r="F39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. Complete every other mandatory field with valid data. | 2. Leave the Outstanding Threshold field empty. | 3. Click **Submit for Approval**.</t>
+          <t xml:space="preserve">1. Open Admin → Branch → Add branch. | 2. Read the Outstanding Threshold field's value without typing anything into it.</t>
         </is>
       </c>
       <c r="G39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The system blocks submission and shows a required-field validation message for Outstanding Threshold.</t>
+          <t xml:space="preserve">The Outstanding Threshold field is not empty — it holds a system-supplied default value.</t>
         </is>
       </c>
       <c r="H39" t="inlineStr" s="2">
@@ -2390,12 +2399,12 @@
       </c>
       <c r="I39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Atomic, Negative-EmptyValues, AssumptionBased, ExpectedImplementation</t>
+          <t xml:space="preserve">Atomic, Positive, ExpectedImplementation</t>
         </is>
       </c>
       <c r="J39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Assumption-based test: US 51489 §2 does not explicitly state whether Child Agencies Threshold Amount is Mandatory or Optional; the live UI marks the field Mandatory with an asterisk. This case assumes Mandatory per the observed UI convention, pending confirmation — see CoverageReport.md §8 for the corresponding Coverage Gap.</t>
+          <t xml:space="preserve">Revised 2026-08-15 by the module owner. This case previously read "blocks submission when empty." That scenario is not reachable: the application pre-fills Outstanding Threshold with a default value as soon as Add Branch opens, so the field is never presented empty and the empty-value case could not be exercised as written. The empty-value scenario is dropped rather than rewritten to clear the field first. The expected value is stated as "not empty" and not as one specific number, because no requirement states what the default should be — see CoverageReport.md §8.</t>
         </is>
       </c>
       <c r="K39" t="inlineStr" s="2">
@@ -3283,36 +3292,36 @@
       </c>
       <c r="B55" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Row action icons match the record's approval state</t>
+          <t xml:space="preserve">Row action icons match the selected Status filter</t>
         </is>
       </c>
       <c r="C55" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Verify that each row offers only the actions valid for its approval state.</t>
+          <t xml:space="preserve">Verify that the row action icons offered in the results grid depend on the selected Status filter (Active / Inactive / Both), not on each record's individual Approval Status.</t>
         </is>
       </c>
       <c r="D55" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">User is logged in as Super Admin and has opened Admin → Branch, with Status set to Both and results displayed.</t>
+          <t xml:space="preserve">User is logged in as Super Admin and has opened Admin → Branch.</t>
         </is>
       </c>
       <c r="E55" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">| Approval Status | Expected icons |
+          <t xml:space="preserve">| Status filter selected | Expected icons (every row) |
 |---|---|
-| Approved | edit pen, thumbs-down |
-| Pending for approval | edit pen, thumbs-up, thumbs-down |
-| Rejected | edit pen, thumbs-up |</t>
+| Active | edit pen, thumbs-down |
+| Inactive | edit pen, thumbs-up, thumbs-down |
+| Both | edit pen, thumbs-up, thumbs-down |</t>
         </is>
       </c>
       <c r="F55" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. Locate a row for each Approval Status in the Test Data. | 2. Read the icons in that row's Actions column.</t>
+          <t xml:space="preserve">1. Select Status **Active**, click **Search**, and read the icons in the Actions column for several rows. | 2. Select Status **Inactive**, click **Search**, and read the icons in the Actions column for several rows. | 3. Select Status **Both**, click **Search**, and read the icons in the Actions column for several rows.</t>
         </is>
       </c>
       <c r="G55" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Each row shows exactly the icons listed for its Approval Status — a record never offers a transition to the state it is already in.</t>
+          <t xml:space="preserve">Every row's icon set matches the Test Data for the Status filter that produced it, regardless of that row's own Approval Status column value.</t>
         </is>
       </c>
       <c r="H55" t="inlineStr" s="2">
@@ -3322,12 +3331,12 @@
       </c>
       <c r="I55" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Atomic, Positive</t>
+          <t xml:space="preserve">Atomic, Positive, BusinessRule</t>
         </is>
       </c>
       <c r="J55" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Pending and Rejected rows may not appear on page 1; page through the results or search for a known record to find one.</t>
+          <t xml:space="preserve">Corrected 2026-08-10 by user instruction — the prior revision of this case tied icons to each row's Approval Status (Approved/Pending/Rejected) rather than to the Status filter selection. That version and its rationale are superseded; the rule verified here is filter-driven, uniform across all rows in a given result set.</t>
         </is>
       </c>
       <c r="K55" t="inlineStr" s="2">
@@ -4675,12 +4684,13 @@
       </c>
       <c r="I78" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Atomic, Security, Regression</t>
+          <t xml:space="preserve">Atomic, Security, Regression, Blocked-NeedsClarification
+**Blocking Reason (2026-08-10):** The module owner dispositioned **FINDING-013** as *"not a bug but business needs"* — returning and pre-filling the stored Branch Email Password is **intended behaviour**. This case's Expected Result asserts the redacted behaviour, which that decision rules out, so as written it can now only ever fail against an application that is behaving as the business intends. Do not execute it as a pass/fail gate, and do not weaken its Expected Result to match the intended behaviour — either would be a Stage 3 change made at the wrong stage. **Required to unblock:** a Stage 3 decision to retire this case, or to rewrite it against the now-intended behaviour (for example, asserting that the field is present and populated, and that no other surface leaks the value), plus documenting the credential-handling expectation in `PRD_UserStories.md` US 8606, which is currently silent on it.</t>
         </is>
       </c>
       <c r="J78" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Asserts the corrected behaviour. Discovery confirmed the stored password is currently returned and populated into this field (FINDING-013), so this case is expected to fail until that is fixed. **Never record the observed password value in a result, defect, or screenshot** — report only whether a recoverable value was present.</t>
+          <t xml:space="preserve">Asserts the corrected behaviour. Discovery confirmed the stored password is returned and populated into this field (FINDING-013) — an observation that remains factually accurate; only its disposition changed, from `Security Concern / Confirmed` to `Observation / Rejected — Confirmed Intended Behaviour`. **Never record the observed password value in a result, defect, or screenshot** — report only whether a recoverable value was present. That rule stands regardless of the disposition.</t>
         </is>
       </c>
       <c r="K78" t="inlineStr" s="2">
@@ -4690,7 +4700,7 @@
       </c>
       <c r="L78" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Rejected</t>
+          <t xml:space="preserve">Rejected — and now also `Blocked — Needs Clarification` (was Rejected on scope grounds alone)</t>
         </is>
       </c>
     </row>
@@ -4929,6 +4939,1776 @@
         </is>
       </c>
     </row>
+    <row r="83">
+      <c r="A83" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">TC-BR-082</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Credit Terms (Days) rejects a value exceeding 7 digits</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Verify that Credit Terms (Days) rejects a numeric value longer than 7 digits.</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">User is logged in as Super Admin and has opened Admin → Branch → Add branch.</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">| Field | Value |
+|---|---|
+| Credit Terms(Days) | 99999999 (8 digits) |</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">1. Enter the Test Data value into Credit Terms (Days). | 2. Move focus away from the field.</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">The system truncates the input to 7 digits, blocks the 8th digit, or displays a validation message that the maximum length is 7 digits.</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">P2</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Atomic, Negative-BoundaryValues</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Added 2026-08-10 from a business clarification that Credit Terms (Days) has a 7-digit maximum — a rule PRD_UserStories.md did not previously state (it documented Credit Terms only as "numeric input only … Mandatory"; the requirement text has now been updated). **The cap itself has not been independently verified live against STG** — it is business-stated, so this case's first execution is also what confirms whether the application actually enforces it. If an 8-digit value is accepted in full, that is a new defect to raise, not a broken test. Leave Automation Rejected until the rule is live-verified, so a fresh unverified expectation is not encoded into the suite ahead of evidence. Related: FINDING-016, where this cap conflicts with Warning Prompt (Days)'s documented 11-digit maximum.</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Approved</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Rejected</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">TC-BR-083</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Auto Reissue is unchecked by default on Add Branch</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Verify that a new Branch form shows the Auto Reissue checkbox unchecked.</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Logged in to Admin (`http://192.168.1.60`). Nothing is saved by this case.</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">1. Open **Admin → Branch**. | 2. Click **Add**. | 3. Find **Auto Reissue** beside Import PNR. | 4. Leave the page without saving.</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">**Auto Reissue** is shown and unchecked. **Auto Reissue Credentials** is not shown.</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">P2</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Atomic, Positive</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Approved</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">TC-BR-084</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Picker is empty on a new Branch with no supplier</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Verify that the Auto Reissue picker offers nothing when the Branch has no supplier.</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">On the Add Branch form, no supplier ticked. Nothing is saved.</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">1. Tick **Auto Reissue**. | 2. Open **Auto Reissue Credentials**. | 3. Leave the page without saving.</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">The picker shows "No results found".</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">P3</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Atomic, Negative-EmptyValues</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Approved</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">TC-BR-085</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">An LCC credential is not offered for Auto Reissue</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Verify that an LCC supplier's credential never appears in the Auto Reissue picker.</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">On the Add Branch form. Nothing is saved.</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">LCC supplier: `AirArabiaEgypt`, with its credential chosen in its Product Access row</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">1. In Product Access, tick **AirArabiaEgypt** and choose its credential. | 2. Tick **Auto Reissue**. | 3. Open **Auto Reissue Credentials**. | 4. Leave the page without saving.</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">The AirArabiaEgypt credential is not offered.</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">P2</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Atomic, Negative, Business-Rule</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Approved</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">TC-BR-086</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">A Galileo PCC credential is offered for Auto Reissue</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Verify that a credential chosen in a supported GDS supplier's PCC tab appears in the picker.</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">On the Add Branch form. Nothing is saved.</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GDS supplier: `Galileo`, PCC tab credential `GalileoLive`</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">1. In Product Access, tick **Galileo**. | 2. In the **Galileo** tab under Airline Supplier credential (PCC), select **GalileoLive**. | 3. Tick **Auto Reissue**. | 4. Open **Auto Reissue Credentials**. | 5. Leave the page without saving.</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">**GalileoLive** is offered.</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">P2</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Atomic, Positive, Business-Rule</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Approved</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">TC-BR-087</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">An Amadeus PCC credential is not offered for Auto Reissue</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Verify that an Amadeus credential never appears in the Auto Reissue picker.</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">On the Add Branch form. Nothing is saved.</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GDS supplier: `Amadeus`, PCC tab credential `Amadeus Live`</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">1. In Product Access, tick **Amadeus**. | 2. In the **Amadeus** tab, select **Amadeus Live**. | 3. Tick **Auto Reissue**. | 4. Open **Auto Reissue Credentials**. | 5. Leave the page without saving.</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">**Amadeus Live** is not offered.</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">P2</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Atomic, Negative, Business-Rule</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Amadeus is a GDS but not on the hard-coded reissue list (`PO-21`). This is spec `S-9` on the screen.</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Approved</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">TC-BR-088</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">A TravelportNdc PCC credential is offered for Auto Reissue</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Verify that a TravelportNdc credential appears in the Auto Reissue picker.</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">On the Add Branch form. A TravelportNdc supplier with at least one credential exists. Nothing is saved.</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">1. In Product Access, tick **TravelportNdc**. | 2. In its PCC tab, select one credential. | 3. Tick **Auto Reissue**. | 4. Open **Auto Reissue Credentials**. | 5. Leave the page without saving.</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">The TravelportNdc credential is offered.</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">P3</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Atomic, Positive, Assumption-based</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Not seen in Discovery. If no TravelportNdc supplier exists on `.60`, record **Blocked**.</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Approved</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">TC-BR-089</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Turn Auto Reissue on for a Branch and save</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Verify that Branch Auto Reissue and one credential are saved and shown again when the Branch is reopened.</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">BRN265 is Approved with Auto Reissue off.</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">| Field | Value |
+|---|---|
+| Branch | BRN265 |
+| Auto Reissue Credentials | `NDCSabre staging` |</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">1. Open **Admin → Branch**, edit BRN265. | 2. Tick **Auto Reissue**. | 3. In **Auto Reissue Credentials**, select **NDCSabre staging**. | 4. Enter a remark. | 5. Click **Send For Approval**. | 6. Approve BRN265 from the Branch grid, entering a remark. | 7. Reopen BRN265.</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">**Auto Reissue** is ticked and **NDCSabre staging** is shown in **Auto Reissue Credentials**.</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Scenario, Positive, Smoke</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Leaves BRN265 on with NDCSabre staging, which is its restore state.</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Approved</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">TC-BR-090</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Branch Auto Reissue change waits for approval</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Verify that a Branch Auto Reissue change sent for approval takes effect only after it is approved.</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">BRN265 is Approved with Auto Reissue on.</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">1. Edit BRN265. | 2. Untick **Auto Reissue**. | 3. Enter a remark and click **Send For Approval**. | 4. Read BRN265's row in the Branch grid. | 5. Approve the row, entering a remark. | 6. Reopen BRN265.</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">After step 4, the row shows **Pending for approval**. After step 5, it shows **Approved**. After step 6, Auto Reissue is unticked.</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">P2</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Scenario, Regression</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Restore afterwards with TC-BR-089.</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Approved</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">TC-BR-091</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Turning Branch Auto Reissue off keeps the saved credentials</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Verify that a Branch's saved credentials return when Auto Reissue is turned on again.</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">BRN265 is Approved with Auto Reissue off, after having had **NDCSabre staging** saved (e.g. after TC-BR-090).</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">1. Edit BRN265. | 2. Tick **Auto Reissue**. | 3. Read **Auto Reissue Credentials**. | 4. Leave the page without saving.</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">The picker already shows **NDCSabre staging**.</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Scenario, Positive, Regression</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Approved</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">TC-BR-092</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Branch Auto Reissue on with no credential shows "Required"</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Verify that the Branch form will not save Auto Reissue on without a credential.</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">BRN265 is Approved.</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">1. Edit BRN265. | 2. Tick **Auto Reissue** if unticked. | 3. Clear **Auto Reissue Credentials**. | 4. Enter a remark. | 5. Click **Send For Approval**.</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">"Required" appears under **Auto Reissue Credentials**. BRN265 is not saved.</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Atomic, Negative-EmptyValues</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Approved</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">TC-BR-093</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Branch update without a remark is refused</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Verify that a Branch Auto Reissue change cannot be sent without a remark.</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">BRN265 is Approved.</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">1. Edit BRN265. | 2. Toggle **Auto Reissue**. | 3. Leave the remark empty. | 4. Click **Send For Approval**.</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">The form shows a message that the remark is required, and BRN265 is not saved.</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">P3</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Atomic, Negative-EmptyValues, Assumption-based</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Discovery always entered a remark, so this was never tried (A-BR-R6-1). If the save goes through, restore BRN265 with TC-BR-089 and report the result.</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Approved</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">TC-BR-094</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Branch API rejects Auto Reissue on with an empty credential list</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Verify that the Branch API rejects Auto Reissue on with no credentials.</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">The `{BRANCH_SAVE_REQUEST}` fixture is loaded in Postman (§0.3). BRN265 is Approved.</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">`autoReissueEnabled`: `true` · `reissueCredentials`: `[]`</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">1. In `{BRANCH_SAVE_REQUEST}`, set `autoReissueEnabled` and `reissueCredentials` to the Test Data values. Leave every other field, including the remark, as captured. | 2. Send the request. | 3. Search BRN265 in Admin → Branch and read its row.</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">The response is **400** with message "Select at least one eligible credential". BRN265 is unchanged.</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">P2</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Atomic, Negative-EmptyValues</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Approved</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">TC-BR-095</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Branch API keeps saved credentials when sent off with others</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Verify that credentials sent with Branch Auto Reissue off are replaced by the saved valid selection.</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">The `{BRANCH_SAVE_REQUEST}` fixture is loaded in Postman (§0.3). BRN265 is Approved, Auto Reissue off, with saved credential `[313]`.</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">`autoReissueEnabled`: `false` · `reissueCredentials`: `[{"credentialId": 315}]`</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">1. In `{BRANCH_SAVE_REQUEST}`, set the two fields to the Test Data values. | 2. Send the request. | 3. Approve BRN265 from the Branch grid, entering a remark. | 4. Read BRN265 with the GET in §0.3.</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">The request succeeds. The GET returns `autoReissueEnabled: false` and `reissueCredentials` `[313]`, not 315.</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">P2</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Atomic, Positive</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">A real save: BRN265 is pending until step 3. Restore afterwards with TC-BR-089.</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Approved</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">TC-BR-096</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Branch API rejects a credential without an ID</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Verify that the Branch API rejects a reissue credential that has no ID.</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">The `{BRANCH_SAVE_REQUEST}` fixture is loaded in Postman (§0.3). BRN265 is Approved.</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">`autoReissueEnabled`: `true` · `reissueCredentials`: `[{}]`</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">1. In `{BRANCH_SAVE_REQUEST}`, set `autoReissueEnabled` and `reissueCredentials` to the Test Data values. Leave every other field, including the remark, as captured. | 2. Send the request. | 3. Search BRN265 in Admin → Branch and read its row.</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">The response is **400** with message "Every auto-reissue credential must have an ID". BRN265 is unchanged.</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">P2</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Atomic, Negative-InvalidInputs</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Approved</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">TC-BR-097</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Branch API rejects an unknown credential ID</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Verify that the Branch API rejects a credential ID that does not exist.</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">The `{BRANCH_SAVE_REQUEST}` fixture is loaded in Postman (§0.3). BRN265 is Approved.</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">`autoReissueEnabled`: `true` · `reissueCredentials`: `[{"credentialId": 999999}]`</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">1. In `{BRANCH_SAVE_REQUEST}`, set `autoReissueEnabled` and `reissueCredentials` to the Test Data values. Leave every other field, including the remark, as captured. | 2. Send the request. | 3. Search BRN265 in Admin → Branch and read its row.</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">The response is **400** with message "Every auto-reissue credential must exist and be active". BRN265 is unchanged.</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">P2</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Atomic, Negative-InvalidInputs</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Approved</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">TC-BR-098</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Branch API rejects duplicate credential IDs</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Verify that the Branch API rejects the same credential sent twice.</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">The `{BRANCH_SAVE_REQUEST}` fixture is loaded in Postman (§0.3). BRN265 is Approved.</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">`autoReissueEnabled`: `true` · `reissueCredentials`: `[{"credentialId": 313}, {"credentialId": 313}]`</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">1. In `{BRANCH_SAVE_REQUEST}`, set `autoReissueEnabled` and `reissueCredentials` to the Test Data values. Leave every other field, including the remark, as captured. | 2. Send the request. | 3. Search BRN265 in Admin → Branch and read its row.</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">The response is **400** with message "Auto-reissue credentials must not contain duplicates". BRN265 is unchanged.</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">P2</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Atomic, Negative-InvalidInputs</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Approved</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">TC-BR-099</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Branch API rejects a credential not assigned to the Branch</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Verify that a Branch cannot be given a reissue credential it is not assigned.</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">The `{BRANCH_SAVE_REQUEST}` fixture is loaded in Postman (§0.3). BRN265 is Approved.</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">`autoReissueEnabled`: `true` · `reissueCredentials`: `[{"credentialId": 287}]` (a supported Galileo credential not in BRN265's Product Access — check first)</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">1. In `{BRANCH_SAVE_REQUEST}`, set `autoReissueEnabled` and `reissueCredentials` to the Test Data values. Leave every other field, including the remark, as captured. | 2. Send the request. | 3. Search BRN265 in Admin → Branch and read its row.</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">The response is **400** with message "Each auto-reissue credential must be mapped to this organization". BRN265 is unchanged.</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Atomic, Negative-InvalidInputs, Permissions</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Approved</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">TC-BR-100</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Branch Auto Reissue does not change its Agencies' checkbox</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Verify that turning Branch Auto Reissue on leaves the Auto Reissue value of its Agencies unchanged.</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">BRN265 has Auto Reissue off. AGN9780 has Auto Reissue off. Both Approved.</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">1. Turn BRN265 Auto Reissue on and approve it (as in TC-BR-089). | 2. Open AGN9780 in Admin → Agency. | 3. Read **Auto Reissue**.</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AGN9780's **Auto Reissue** is still unticked.</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Atomic, Integration</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Approved</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">TC-BR-101</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Admin shows Reissue for a Branch booking when Branch Auto Reissue is on</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Verify that the Admin Itinerary shows Reissue on a Branch-owned booking when the Branch has Auto Reissue on.</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">BRN265 has Auto Reissue on (Approved). Booking `NDCEG-BR-F260916ENYOeQ` (owned by BRN265, Booked) is not locked by another user.</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">1. Open **Booking-Mid Office → Search Booking** (`/booking/search-booking`). | 2. Click the **Flight** tab. | 3. Enter Booking Reference `NDCEG-BR-F260916ENYOeQ` and click **Search**. | 4. Open the booking from the result row. | 5. Click the lock icon on the **Created By** card. | 6. Click **View Passenger Details**.</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">The **Reissue** button is shown.</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Atomic, Positive, Smoke</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Never click **Reissue**, **Release PNR** or **Void / Cancel**. Status **Booked** in Booking Information is the condition, not the "Ticketed Document" bar (`PO-24`).</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Approved</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">TC-BR-102</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Admin hides Reissue for a Branch booking when Branch Auto Reissue is off</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Verify that the Admin Itinerary hides Reissue on a Branch-owned booking when the Branch has Auto Reissue off.</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">BRN265 has Auto Reissue off (Approved). Booking `NDCEG-BR-F260916ENYOeQ` is not locked by another user.</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">1. Open **Booking-Mid Office → Search Booking** (`/booking/search-booking`). | 2. Click the **Flight** tab. | 3. Enter Booking Reference `NDCEG-BR-F260916ENYOeQ` and click **Search**. | 4. Open the booking from the result row. | 5. Click the lock icon on the **Created By** card. | 6. Click **View Passenger Details**.</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">The **Reissue** button is not shown. **Manual Reissue** is still shown.</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Atomic, Negative, Smoke</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Never click **Reissue**, **Release PNR** or **Void / Cancel**. Status **Booked** in Booking Information is the condition, not the "Ticketed Document" bar (`PO-24`). Read BRN265's flag just before this check: it was changed by hand during Discovery.</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Approved</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">TC-BR-103</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Reissue shows on a Branch booking whose credential is not selected</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Verify that the Branch booking's Reissue button depends on the checkbox, not on the selected credentials.</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">BRN265 has Auto Reissue on with only **NDCSabre staging** (313) selected. Booking `NDCEG-BR-F260916ENYOeQ` is on **Sabre Staging** (315).</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">1. Open **Booking-Mid Office → Search Booking** (`/booking/search-booking`). | 2. Click the **Flight** tab. | 3. Enter Booking Reference `NDCEG-BR-F260916ENYOeQ` and click **Search**. | 4. Open the booking from the result row. | 5. Click the lock icon on the **Created By** card. | 6. Click **View Passenger Details**.</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">The **Reissue** button is shown.</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">P3</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Atomic, Business-Rule</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Intended (`PO-22`). The credential is checked only when Reissue is clicked, in the `reissue-flow` scope. Never click **Reissue**, **Release PNR** or **Void / Cancel**. Status **Booked** in Booking Information is the condition, not the "Ticketed Document" bar (`PO-24`).</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Approved</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">TC-BR-104</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Agency Auto Reissue off does not hide Reissue on a Branch booking</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Verify that an Agency's Auto Reissue value does not affect a booking owned by its Branch.</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">BRN265 has Auto Reissue on. AGN9780 has Auto Reissue off. Both Approved.</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">1. Open **Booking-Mid Office → Search Booking** (`/booking/search-booking`). | 2. Click the **Flight** tab. | 3. Enter Booking Reference `NDCEG-BR-F260916ENYOeQ` and click **Search**. | 4. Open the booking from the result row. | 5. Click the lock icon on the **Created By** card. | 6. Click **View Passenger Details**.</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">The **Reissue** button is shown.</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">P2</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Atomic, Integration</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Never click **Reissue**, **Release PNR** or **Void / Cancel**. Status **Booked** in Booking Information is the condition, not the "Ticketed Document" bar (`PO-24`).</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Approved</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">TC-BR-105</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Reading the Branch drops a credential that became invalid</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Verify that a saved Branch credential that became invalid is removed on read, while Auto Reissue stays on.</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">BRN265 has Auto Reissue on and a saved credential that has since become inactive, unassigned or unsupported.</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">1. Reopen BRN265. | 2. Read **Auto Reissue** and **Auto Reissue Credentials**.</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">The invalid credential is no longer listed. **Auto Reissue** stays ticked.</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">P3</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Atomic, Assumption-based</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">**Needs a supplier or credential change this run is not granted (RISK-BR-11).** **TC-BR-110 sets up this state** (with the user's go-ahead). Otherwise record **Blocked**.</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Approved</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">TC-BR-106</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Updating a Branch without touching Auto Reissue still works</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Verify that an ordinary Branch update still saves and leaves Auto Reissue unchanged.</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">BRN265 is Approved. Its Auto Reissue value and credentials are recorded.</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">1. Edit BRN265. | 2. Change only the remark text. | 3. Click **Send For Approval**. | 4. Approve BRN265 from the grid, entering a remark. | 5. Reopen BRN265.</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">The update is saved and approved. **Auto Reissue** and **Auto Reissue Credentials** are the same as recorded.</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">P2</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Atomic, Regression, Smoke</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Approved</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">TC-BR-107</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Create a Branch with Auto Reissue on</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Verify that a new Branch can be created with Auto Reissue on and a credential.</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">**The user has been asked and agrees to create a new Branch** (allowed after asking — user, 2026-09-24). The Branch's other mandatory fields and one supported GDS supplier are ready.</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">| Field | Value |
+|---|---|
+| Branch name | `RUN006_AR_Branch` |
+| Supplier | Galileo, PCC tab `GalileoLive` |</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">1. Open **Admin → Branch → Add**. | 2. Fill the mandatory fields with Test Data. | 3. Tick **Auto Reissue** and select **GalileoLive**. | 4. Click **Send For Approval**. | 5. Approve the new Branch from the grid, entering a remark. | 6. Reopen the new Branch.</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">The new Branch shows **Auto Reissue** ticked with **GalileoLive**.</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">P3</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Scenario, Positive</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">**Creates a lasting record on STG.** Ask the user before running it. Without their agreement, record **Blocked — awaiting user agreement**.</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Approved</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">TC-BR-108</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Agency Portal does not list its Branch's own bookings</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Verify that an Agency's Portal login cannot see a booking owned by its parent Branch.</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">The AGN9780 Portal login is available. Booking `NDCEG-BR-F260916ENYOeQ` is owned by BRN265.</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">1. Log in to the Portal (`http://192.168.1.60:9500`) with agency code `AGN9780`. | 2. Open **My Booking** and click **Search**. | 3. Look for `NDCEG-BR-F260916ENYOeQ` in the results.</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">`NDCEG-BR-F260916ENYOeQ` is not listed.</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">P3</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Atomic, Permissions, Assumption-based</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">The user's statement (`PO-26`), not yet observed.</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Approved</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">TC-BR-109</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">A Branch can have a supplier its Agency doesn't have</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Verify that a Branch can keep a supplier that is not assigned to its Agency.</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">BRN265 has at least one supplier (e.g. NDCsbr) that is **not** ticked in AGN9780's Product Access. Nothing is saved by this case.</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">1. Open BRN265 for edit and record its suppliers. | 2. Leave BRN265 without saving. | 3. Open AGN9780 for edit and read **Product Access Details**. | 4. Leave AGN9780 without saving.</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">BRN265 lists the supplier. AGN9780 lists it as **not assigned**. Both records stay Approved.</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">P2</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Atomic, Integration</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Branch and Agency each have their own CRUD (`PO-27`). The other direction is TC-AGENCY-091.</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Approved</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">TC-BR-110</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">An inactive credential leaves the Branch's Auto Reissue picker</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Verify that a reissue credential made inactive is dropped from the Branch's saved selection and picker, while Auto Reissue stays on.</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">A supported GDS credential `{CRED}` that no other organisation uses, chosen in BRN265's PCC tab. BRN265 has Auto Reissue on with `{CRED}` selected, Approved.</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">1. Open **Master → Supplier → Supplier Credentials** and search `{CRED}`. | 2. Edit `{CRED}`, set its status to **Inactive**, and save. | 3. Open BRN265 for edit (Admin → Branch). | 4. Read **Auto Reissue** and **Auto Reissue Credentials**. | 5. Open **Auto Reissue Credentials** and read the options. | 6. Leave the form without saving. | 7. Set `{CRED}` back to **Active** and save.</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">After step 4, `{CRED}` is no longer in the saved selection, and **Auto Reissue** is still ticked. After step 5, `{CRED}` is not offered.</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Scenario, Negative, Integration</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Ask the user before running this case. It changes **shared master data** (Master → Supplier) on staging, which affects every organisation that uses it. Use only a supplier/credential that no other organisation uses, record the grant in the run's `SafetyAuthorizations.json` first, and **set it back to Active at the end**. Spec §4. Can share `{CRED}` and the same inactive window with TC-AGENCY-092. Afterwards restore BRN265 to NDCSabre staging (313).</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Approved</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">TC-BR-111</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">What the Branch's Auto Reissue picker shows when the supplier is made inactive</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Find out what happens to the Branch's Auto Reissue selection and picker when the credential's supplier is made inactive.</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">As TC-BR-110, using a GDS supplier `{SUP}` that no other organisation uses. BRN265 has Auto Reissue on with a `{SUP}` credential selected, Approved.</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">1. Open **Master → Supplier → Supplier** and search `{SUP}`. | 2. Edit `{SUP}`, set its status to **Inactive**, and save. | 3. Open BRN265 for edit. | 4. Read **Auto Reissue**, **Auto Reissue Credentials** and **Product Access Details**. | 5. Open **Auto Reissue Credentials** and read the options. | 6. Leave the form without saving. | 7. Set `{SUP}` back to **Active** and save.</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">The tester records what is shown in steps 4–5, and the reviewer confirms whether it is intended. Spec §4 suggests the credential is dropped and not offered, with Auto Reissue still ticked.</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">P2</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Scenario, Exploratory, Integration</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Ask the user before running this case. It changes **shared master data** (Master → Supplier) on staging, which affects every organisation that uses it. Use only a supplier/credential that no other organisation uses, record the grant in the run's `SafetyAuthorizations.json` first, and **set it back to Active at the end**. Exploratory: the specification covers an inactive credential, not an inactive supplier.</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Approved</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">TC-BR-112</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Admin hides Reissue for a Branch booking on hold</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Verify that the Admin Itinerary does not show Reissue for a Branch booking whose status is On Hold.</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">BRN265 has Auto Reissue on (Approved). Booking `NDCEG-BR-F251103CdegUo` (BRN265, On Hold) is not locked by another user.</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">1. Open **Booking-Mid Office → Search Booking** (`/booking/search-booking`). | 2. Click the **Flight** tab. | 3. Enter Booking Reference `NDCEG-BR-F251103CdegUo` and click **Search**. | 4. Open the booking from the result row. | 5. Click the lock icon on the **Created By** card. | 6. Click **View Passenger Details**.</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">The **Reissue** button is not shown.</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">P2</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Atomic, Negative</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Added 2026-09-25 with the booking the user supplied. Only Status **Booked** shows Reissue (spec §5, `PO-24`). Never click **Reissue**, **Release PNR** or **Void / Cancel**.</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Approved</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Pending</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/platform_core_data/modules/branch/test_design/TestCases_Branch.xlsx
+++ b/platform_core_data/modules/branch/test_design/TestCases_Branch.xlsx
@@ -6040,12 +6040,12 @@
       </c>
       <c r="D102" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BRN265 has Auto Reissue on (Approved). Booking `NDCEG-BR-F260916ENYOeQ` (owned by BRN265, Booked) is not locked by another user.</t>
+          <t xml:space="preserve">BRN265 has Auto Reissue on (Approved) **with Sabre Staging (315) — the booking's credential — in the selection (`PO-28`)**. Booking `NDCEG-BR-F260926PwYMR2` (owned by BRN265, credential 315, Booked) is not locked by another user.</t>
         </is>
       </c>
       <c r="F102" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. Open **Booking-Mid Office → Search Booking** (`/booking/search-booking`). | 2. Click the **Flight** tab. | 3. Enter Booking Reference `NDCEG-BR-F260916ENYOeQ` and click **Search**. | 4. Open the booking from the result row. | 5. Click the lock icon on the **Created By** card. | 6. Click **View Passenger Details**.</t>
+          <t xml:space="preserve">1. Open **Booking-Mid Office → Search Booking** (`/booking/search-booking`). | 2. Click the **Flight** tab. | 3. Enter Booking Reference `NDCEG-BR-F260926PwYMR2` and click **Search**. | 4. Open the booking from the result row. | 5. Click the lock icon on the **Created By** card. | 6. Click **View Passenger Details**.</t>
         </is>
       </c>
       <c r="G102" t="inlineStr" s="2">
@@ -6097,17 +6097,17 @@
       </c>
       <c r="D103" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BRN265 has Auto Reissue off (Approved). Booking `NDCEG-BR-F260916ENYOeQ` is not locked by another user.</t>
+          <t xml:space="preserve">BRN265 has Auto Reissue off (Approved). Booking `NDCEG-BR-F260926PwYMR2` is not locked by another user.</t>
         </is>
       </c>
       <c r="F103" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. Open **Booking-Mid Office → Search Booking** (`/booking/search-booking`). | 2. Click the **Flight** tab. | 3. Enter Booking Reference `NDCEG-BR-F260916ENYOeQ` and click **Search**. | 4. Open the booking from the result row. | 5. Click the lock icon on the **Created By** card. | 6. Click **View Passenger Details**.</t>
+          <t xml:space="preserve">1. Open **Booking-Mid Office → Search Booking** (`/booking/search-booking`). | 2. Click the **Flight** tab. | 3. Enter Booking Reference `NDCEG-BR-F260926PwYMR2` and click **Search**. | 4. Open the booking from the result row. | 5. Click the lock icon on the **Created By** card. | 6. Click **View Passenger Details**.</t>
         </is>
       </c>
       <c r="G103" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The **Reissue** button is not shown. **Manual Reissue** is still shown.</t>
+          <t xml:space="preserve">The **Reissue** button is not shown. **Manual Reissue is out of scope** for this story (`PO-29`, user decision 2026-09-27) and is not asserted here.</t>
         </is>
       </c>
       <c r="H103" t="inlineStr" s="2">
@@ -6144,42 +6144,42 @@
       </c>
       <c r="B104" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Reissue shows on a Branch booking whose credential is not selected</t>
+          <t xml:space="preserve">Reissue is hidden on a Branch booking whose credential is not selected</t>
         </is>
       </c>
       <c r="C104" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Verify that the Branch booking's Reissue button depends on the checkbox, not on the selected credentials.</t>
+          <t xml:space="preserve">Verify that the Branch booking's Reissue button requires **both** the checkbox on **and** a selected credential matching the credential the PNR was booked on (`PO-28`).</t>
         </is>
       </c>
       <c r="D104" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BRN265 has Auto Reissue on with only **NDCSabre staging** (313) selected. Booking `NDCEG-BR-F260916ENYOeQ` is on **Sabre Staging** (315).</t>
+          <t xml:space="preserve">BRN265 has Auto Reissue on with only **NDCSabre staging** (313) selected. Booking `NDCEG-BR-F260926PwYMR2` is on **Sabre Staging** (315).</t>
         </is>
       </c>
       <c r="F104" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. Open **Booking-Mid Office → Search Booking** (`/booking/search-booking`). | 2. Click the **Flight** tab. | 3. Enter Booking Reference `NDCEG-BR-F260916ENYOeQ` and click **Search**. | 4. Open the booking from the result row. | 5. Click the lock icon on the **Created By** card. | 6. Click **View Passenger Details**.</t>
+          <t xml:space="preserve">1. Open **Booking-Mid Office → Search Booking** (`/booking/search-booking`). | 2. Click the **Flight** tab. | 3. Enter Booking Reference `NDCEG-BR-F260926PwYMR2` and click **Search**. | 4. Open the booking from the result row. | 5. Click the lock icon on the **Created By** card. | 6. Click **View Passenger Details**.</t>
         </is>
       </c>
       <c r="G104" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The **Reissue** button is shown.</t>
+          <t xml:space="preserve">The **Reissue** button is **not** shown (`actionsDetails.canAutoReissue: false`). **Manual Reissue is out of scope** for this story (`PO-29`, user decision 2026-09-27) and is not asserted here.</t>
         </is>
       </c>
       <c r="H104" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">P3</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="I104" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Atomic, Business-Rule</t>
+          <t xml:space="preserve">Atomic, Negative, Business-Rule</t>
         </is>
       </c>
       <c r="J104" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Intended (`PO-22`). The credential is checked only when Reissue is clicked, in the `reissue-flow` scope. Never click **Reissue**, **Release PNR** or **Void / Cancel**. Status **Booked** in Booking Information is the condition, not the "Ticketed Document" bar (`PO-24`).</t>
+          <t xml:space="preserve">**Rev 2, 2026-09-27 — expected result inverted under `PO-28`** (product owner: the button needs the checkbox **and** a selected credential matching the PNR's booking credential). Rev 1 expected "shown" under the now-superseded `PO-22`. Already observed this way in run-007 Discovery `DS-2` (`reissue-flow/discovery/evidence/cl1-check.json`). Booking reference changed from `NDCEG-BR-F260916ENYOeQ` to `NDCEG-BR-F260926PwYMR2` per run-007 `D-13` (the old PNR was exchanged outside the app and is no longer reissuable). Restore BRN265's selection to include 315 afterwards. Never click **Reissue**, **Release PNR** or **Void / Cancel**. Status **Booked** in Booking Information is the condition, not the "Ticketed Document" bar (`PO-24`).</t>
         </is>
       </c>
       <c r="K104" t="inlineStr" s="2">
@@ -6211,12 +6211,12 @@
       </c>
       <c r="D105" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BRN265 has Auto Reissue on. AGN9780 has Auto Reissue off. Both Approved.</t>
+          <t xml:space="preserve">BRN265 has Auto Reissue on **with Sabre Staging (315) — the booking's credential — in the selection (`PO-28`)**. AGN9780 has Auto Reissue off. Both Approved.</t>
         </is>
       </c>
       <c r="F105" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. Open **Booking-Mid Office → Search Booking** (`/booking/search-booking`). | 2. Click the **Flight** tab. | 3. Enter Booking Reference `NDCEG-BR-F260916ENYOeQ` and click **Search**. | 4. Open the booking from the result row. | 5. Click the lock icon on the **Created By** card. | 6. Click **View Passenger Details**.</t>
+          <t xml:space="preserve">1. Open **Booking-Mid Office → Search Booking** (`/booking/search-booking`). | 2. Click the **Flight** tab. | 3. Enter Booking Reference `NDCEG-BR-F260926PwYMR2` and click **Search**. | 4. Open the booking from the result row. | 5. Click the lock icon on the **Created By** card. | 6. Click **View Passenger Details**.</t>
         </is>
       </c>
       <c r="G105" t="inlineStr" s="2">
@@ -6670,7 +6670,7 @@
       </c>
       <c r="D113" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BRN265 has Auto Reissue on (Approved). Booking `NDCEG-BR-F251103CdegUo` (BRN265, On Hold) is not locked by another user.</t>
+          <t xml:space="preserve">BRN265 has Auto Reissue on (Approved) **with that booking's credential in the selection (`PO-28`)**, so status is the only condition left unmet. Booking `NDCEG-BR-F251103CdegUo` (BRN265, On Hold) is not locked by another user.</t>
         </is>
       </c>
       <c r="F113" t="inlineStr" s="2">

--- a/platform_core_data/modules/branch/test_design/TestCases_Branch.xlsx
+++ b/platform_core_data/modules/branch/test_design/TestCases_Branch.xlsx
@@ -60,7 +60,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L113"/>
+  <dimension ref="A1:L115"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -6040,12 +6040,12 @@
       </c>
       <c r="D102" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BRN265 has Auto Reissue on (Approved) **with Sabre Staging (315) — the booking's credential — in the selection (`PO-28`)**. Booking `NDCEG-BR-F260926PwYMR2` (owned by BRN265, credential 315, Booked) is not locked by another user.</t>
+          <t xml:space="preserve">All six `PO-30` conditions hold. BRN265 has Auto Reissue on (Approved) **with Sabre Staging (315) — the booking's credential — in the selection (`PO-28`)**. Booking `NDCEG-BR-F260926PwYMR2` (owned by BRN265, supplier **Sabre** — a reissue-capable GDS — credential 315, Booking Type **Online**, Status **Booked**, status bar **"Ticketed Document"**) is not locked by another user; step 6 locks it to you.</t>
         </is>
       </c>
       <c r="F102" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. Open **Booking-Mid Office → Search Booking** (`/booking/search-booking`). | 2. Click the **Flight** tab. | 3. Enter Booking Reference `NDCEG-BR-F260926PwYMR2` and click **Search**. | 4. Open the booking from the result row. | 5. Click the lock icon on the **Created By** card. | 6. Click **View Passenger Details**.</t>
+          <t xml:space="preserve">1. Open **Booking-Mid Office → Search Booking** (`/booking/search-booking`). | 2. Click the **Flight** tab. | 3. Enter Booking Reference `NDCEG-BR-F260926PwYMR2` and click **Search**. | 4. Open the booking from the result row. | 5. Confirm Booking Information reads Status **Booked** and Booking Type **Online**, and the status bar reads **"Ticketed Document"**. If any differs, stop and record **Blocked — precondition not met**. | 6. Click the lock icon on the **Created By** card and confirm it shows your name. | 7. Click **View Passenger Details**.</t>
         </is>
       </c>
       <c r="G102" t="inlineStr" s="2">
@@ -6065,12 +6065,12 @@
       </c>
       <c r="J102" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Never click **Reissue**, **Release PNR** or **Void / Cancel**. Status **Booked** in Booking Information is the condition, not the "Ticketed Document" bar (`PO-24`).</t>
+          <t xml:space="preserve">**Rev 2, 2026-10-01 — preconditions brought under `PO-30`** (user: the button needs all six conditions). The booking must also be **Online**, on a reissue-capable GDS, Status **Booked** with the **"Ticketed Document"** bar, and **locked by you**; step 5 confirms the status, booking type and bar before the check. Expected result unchanged. Never click **Reissue**, **Release PNR** or **Void / Cancel**. Status **Booked** in Booking Information **and** the status bar reading **"Ticketed Document"** are both required (`PO-30`, which withdraws `PO-24`'s first sentence).</t>
         </is>
       </c>
       <c r="K102" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Approved</t>
+          <t xml:space="preserve">Pending</t>
         </is>
       </c>
       <c r="L102" t="inlineStr" s="2">
@@ -6097,12 +6097,12 @@
       </c>
       <c r="D103" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BRN265 has Auto Reissue off (Approved). Booking `NDCEG-BR-F260926PwYMR2` is not locked by another user.</t>
+          <t xml:space="preserve">BRN265 has Auto Reissue off (Approved), so condition (1) of `PO-30` is the only one unmet. Its saved selection still contains Sabre Staging (315) (spec `S-7`). Booking `NDCEG-BR-F260926PwYMR2` (owned by BRN265, supplier **Sabre** — a reissue-capable GDS — credential 315, Booking Type **Online**, Status **Booked**, status bar **"Ticketed Document"**) is not locked by another user; step 6 locks it to you.</t>
         </is>
       </c>
       <c r="F103" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. Open **Booking-Mid Office → Search Booking** (`/booking/search-booking`). | 2. Click the **Flight** tab. | 3. Enter Booking Reference `NDCEG-BR-F260926PwYMR2` and click **Search**. | 4. Open the booking from the result row. | 5. Click the lock icon on the **Created By** card. | 6. Click **View Passenger Details**.</t>
+          <t xml:space="preserve">1. Open **Booking-Mid Office → Search Booking** (`/booking/search-booking`). | 2. Click the **Flight** tab. | 3. Enter Booking Reference `NDCEG-BR-F260926PwYMR2` and click **Search**. | 4. Open the booking from the result row. | 5. Confirm Booking Information reads Status **Booked** and Booking Type **Online**, and the status bar reads **"Ticketed Document"**. If any differs, stop and record **Blocked — precondition not met**. | 6. Click the lock icon on the **Created By** card and confirm it shows your name. | 7. Click **View Passenger Details**.</t>
         </is>
       </c>
       <c r="G103" t="inlineStr" s="2">
@@ -6122,12 +6122,12 @@
       </c>
       <c r="J103" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Never click **Reissue**, **Release PNR** or **Void / Cancel**. Status **Booked** in Booking Information is the condition, not the "Ticketed Document" bar (`PO-24`). Read BRN265's flag just before this check: it was changed by hand during Discovery.</t>
+          <t xml:space="preserve">**Rev 2, 2026-10-01 — preconditions brought under `PO-30`**: the other five conditions (credential in the selection, Booked + "Ticketed Document", Online, locked by you, reissue-capable GDS) are stated and step 5 confirms them, so the checkbox is the only cause of the hidden button. Expected result unchanged. Never click **Reissue**, **Release PNR** or **Void / Cancel**. Status **Booked** in Booking Information **and** the status bar reading **"Ticketed Document"** are both required (`PO-30`, which withdraws `PO-24`'s first sentence). Read BRN265's flag just before this check: it was changed by hand during Discovery.</t>
         </is>
       </c>
       <c r="K103" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Approved</t>
+          <t xml:space="preserve">Pending</t>
         </is>
       </c>
       <c r="L103" t="inlineStr" s="2">
@@ -6154,12 +6154,12 @@
       </c>
       <c r="D104" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BRN265 has Auto Reissue on with only **NDCSabre staging** (313) selected. Booking `NDCEG-BR-F260926PwYMR2` is on **Sabre Staging** (315).</t>
+          <t xml:space="preserve">BRN265 has Auto Reissue on with only **NDCSabre staging** (313) selected, so condition (2) of `PO-30` is the only one unmet. Booking `NDCEG-BR-F260926PwYMR2` is on **Sabre Staging** (315); it is owned by BRN265, supplier **Sabre**, Booking Type **Online**, Status **Booked**, status bar **"Ticketed Document"**, and is not locked by another user; step 6 locks it to you.</t>
         </is>
       </c>
       <c r="F104" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. Open **Booking-Mid Office → Search Booking** (`/booking/search-booking`). | 2. Click the **Flight** tab. | 3. Enter Booking Reference `NDCEG-BR-F260926PwYMR2` and click **Search**. | 4. Open the booking from the result row. | 5. Click the lock icon on the **Created By** card. | 6. Click **View Passenger Details**.</t>
+          <t xml:space="preserve">1. Open **Booking-Mid Office → Search Booking** (`/booking/search-booking`). | 2. Click the **Flight** tab. | 3. Enter Booking Reference `NDCEG-BR-F260926PwYMR2` and click **Search**. | 4. Open the booking from the result row. | 5. Confirm Booking Information reads Status **Booked** and Booking Type **Online**, and the status bar reads **"Ticketed Document"**. If any differs, stop and record **Blocked — precondition not met**. | 6. Click the lock icon on the **Created By** card and confirm it shows your name. | 7. Click **View Passenger Details**.</t>
         </is>
       </c>
       <c r="G104" t="inlineStr" s="2">
@@ -6179,12 +6179,12 @@
       </c>
       <c r="J104" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">**Rev 2, 2026-09-27 — expected result inverted under `PO-28`** (product owner: the button needs the checkbox **and** a selected credential matching the PNR's booking credential). Rev 1 expected "shown" under the now-superseded `PO-22`. Already observed this way in run-007 Discovery `DS-2` (`reissue-flow/discovery/evidence/cl1-check.json`). Booking reference changed from `NDCEG-BR-F260916ENYOeQ` to `NDCEG-BR-F260926PwYMR2` per run-007 `D-13` (the old PNR was exchanged outside the app and is no longer reissuable). Restore BRN265's selection to include 315 afterwards. Never click **Reissue**, **Release PNR** or **Void / Cancel**. Status **Booked** in Booking Information is the condition, not the "Ticketed Document" bar (`PO-24`).</t>
+          <t xml:space="preserve">**Rev 3, 2026-10-01 — preconditions brought under `PO-30`**: the other five conditions are stated and step 5 confirms them, so the unselected credential is the only cause. Expected result unchanged; `PO-28` is now condition (2) of `PO-30`. **Rev 2, 2026-09-27 — expected result inverted under `PO-28`** (product owner: the button needs the checkbox **and** a selected credential matching the PNR's booking credential). Rev 1 expected "shown" under the now-superseded `PO-22`. Already observed this way in run-007 Discovery `DS-2` (`reissue-flow/discovery/evidence/cl1-check.json`). Booking reference changed from `NDCEG-BR-F260916ENYOeQ` to `NDCEG-BR-F260926PwYMR2` per run-007 `D-13` (the old PNR was exchanged outside the app and is no longer reissuable). Restore BRN265's selection to include 315 afterwards. Never click **Reissue**, **Release PNR** or **Void / Cancel**. Status **Booked** in Booking Information **and** the status bar reading **"Ticketed Document"** are both required (`PO-30`, which withdraws `PO-24`'s first sentence).</t>
         </is>
       </c>
       <c r="K104" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Approved</t>
+          <t xml:space="preserve">Pending</t>
         </is>
       </c>
       <c r="L104" t="inlineStr" s="2">
@@ -6211,12 +6211,12 @@
       </c>
       <c r="D105" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BRN265 has Auto Reissue on **with Sabre Staging (315) — the booking's credential — in the selection (`PO-28`)**. AGN9780 has Auto Reissue off. Both Approved.</t>
+          <t xml:space="preserve">BRN265 has Auto Reissue on **with Sabre Staging (315) — the booking's credential — in the selection (`PO-28`)**. AGN9780 has Auto Reissue off. Both Approved. All six `PO-30` conditions hold for BRN265. Booking `NDCEG-BR-F260926PwYMR2` (owned by BRN265, supplier **Sabre** — a reissue-capable GDS — credential 315, Booking Type **Online**, Status **Booked**, status bar **"Ticketed Document"**) is not locked by another user; step 6 locks it to you.</t>
         </is>
       </c>
       <c r="F105" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. Open **Booking-Mid Office → Search Booking** (`/booking/search-booking`). | 2. Click the **Flight** tab. | 3. Enter Booking Reference `NDCEG-BR-F260926PwYMR2` and click **Search**. | 4. Open the booking from the result row. | 5. Click the lock icon on the **Created By** card. | 6. Click **View Passenger Details**.</t>
+          <t xml:space="preserve">1. Open **Booking-Mid Office → Search Booking** (`/booking/search-booking`). | 2. Click the **Flight** tab. | 3. Enter Booking Reference `NDCEG-BR-F260926PwYMR2` and click **Search**. | 4. Open the booking from the result row. | 5. Confirm Booking Information reads Status **Booked** and Booking Type **Online**, and the status bar reads **"Ticketed Document"**. If any differs, stop and record **Blocked — precondition not met**. | 6. Click the lock icon on the **Created By** card and confirm it shows your name. | 7. Click **View Passenger Details**.</t>
         </is>
       </c>
       <c r="G105" t="inlineStr" s="2">
@@ -6236,12 +6236,12 @@
       </c>
       <c r="J105" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Never click **Reissue**, **Release PNR** or **Void / Cancel**. Status **Booked** in Booking Information is the condition, not the "Ticketed Document" bar (`PO-24`).</t>
+          <t xml:space="preserve">**Rev 2, 2026-10-01 — preconditions brought under `PO-30`** (user: the button needs all six conditions). The booking must also be **Online**, on a reissue-capable GDS, Status **Booked** with the **"Ticketed Document"** bar, and **locked by you**; step 5 confirms them. Expected result unchanged. Never click **Reissue**, **Release PNR** or **Void / Cancel**. Status **Booked** in Booking Information **and** the status bar reading **"Ticketed Document"** are both required (`PO-30`, which withdraws `PO-24`'s first sentence).</t>
         </is>
       </c>
       <c r="K105" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Approved</t>
+          <t xml:space="preserve">Pending</t>
         </is>
       </c>
       <c r="L105" t="inlineStr" s="2">
@@ -6665,45 +6665,159 @@
       </c>
       <c r="C113" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Verify that the Admin Itinerary does not show Reissue for a Branch booking whose status is On Hold.</t>
+          <t xml:space="preserve">Verify that the Admin Itinerary does not show Reissue for a Branch booking that is not Status **Booked** with the **"Ticketed Document"** status bar — here, On Hold (`PO-30` condition 3).</t>
         </is>
       </c>
       <c r="D113" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BRN265 has Auto Reissue on (Approved) **with that booking's credential in the selection (`PO-28`)**, so status is the only condition left unmet. Booking `NDCEG-BR-F251103CdegUo` (BRN265, On Hold) is not locked by another user.</t>
+          <t xml:space="preserve">BRN265 has Auto Reissue on (Approved) **with that booking's credential in the selection (`PO-28`)**, so condition (3) of `PO-30` is the only one left unmet. Booking `NDCEG-BR-F251103CdegUo` (BRN265, Booking Type **Online**, Status **On Hold**, status bar **"On Hold"**) is not locked by another user; step 6 locks it to you.</t>
         </is>
       </c>
       <c r="F113" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. Open **Booking-Mid Office → Search Booking** (`/booking/search-booking`). | 2. Click the **Flight** tab. | 3. Enter Booking Reference `NDCEG-BR-F251103CdegUo` and click **Search**. | 4. Open the booking from the result row. | 5. Click the lock icon on the **Created By** card. | 6. Click **View Passenger Details**.</t>
+          <t xml:space="preserve">1. Open **Booking-Mid Office → Search Booking** (`/booking/search-booking`). | 2. Click the **Flight** tab. | 3. Enter Booking Reference `NDCEG-BR-F251103CdegUo` and click **Search**. | 4. Open the booking from the result row. | 5. Read Booking Information → **Status** and **Booking Type**, and the status bar. | 6. Click the lock icon on the **Created By** card and confirm it shows your name. | 7. Click **View Passenger Details**.</t>
         </is>
       </c>
       <c r="G113" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">Status reads **On Hold** (not Booked) and the status bar does **not** read "Ticketed Document". The **Reissue** button is not shown.</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">P2</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Atomic, Negative</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">**Rev 2, 2026-10-01 — asserts the combined status condition under `PO-30`**: only Status **Booked** **and** the **"Ticketed Document"** bar show Reissue (spec §5, `PO-30`; `PO-24`'s "Booked, not the bar" sentence is withdrawn). Step 5 and the Expected Result now read both. This booking fails both halves; no Booked booking without the "Ticketed Document" bar is available, so the bar half is not isolated. Added 2026-09-25 with the booking the user supplied. Never click **Reissue**, **Release PNR** or **Void / Cancel**.</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Pending</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">TC-BR-113</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Admin hides Reissue for a Branch booking not locked by the current user</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Verify that the Admin Itinerary does not show Reissue on a Branch booking until the current user holds its lock (`PO-30` condition 5).</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">BRN265 has Auto Reissue on (Approved) **with Sabre Staging (315) — the booking's credential — in the selection (`PO-28`)**. Booking `NDCEG-BR-F260926PwYMR2` (owned by BRN265, supplier **Sabre**, credential 315, Booking Type **Online**, Status **Booked**, status bar **"Ticketed Document"**) is **not locked by anyone**: the **Created By** card shows the open lock icon. If you still hold it from an earlier case, release it from the lock icon (never with **Release PNR**).</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">1. Open **Booking-Mid Office → Search Booking** (`/booking/search-booking`). | 2. Click the **Flight** tab. | 3. Enter Booking Reference `NDCEG-BR-F260926PwYMR2` and click **Search**. | 4. Open the booking from the result row. | 5. Confirm Booking Information reads Status **Booked** and Booking Type **Online**, the status bar reads **"Ticketed Document"**, and the **Created By** lock is open. | 6. **Do not** click the lock icon. Click **View Passenger Details**.</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">The **Reissue** button is not shown.</t>
         </is>
       </c>
-      <c r="H113" t="inlineStr" s="2">
+      <c r="H114" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">P2</t>
         </is>
       </c>
-      <c r="I113" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">Atomic, Negative</t>
-        </is>
-      </c>
-      <c r="J113" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">Added 2026-09-25 with the booking the user supplied. Only Status **Booked** shows Reissue (spec §5, `PO-24`). Never click **Reissue**, **Release PNR** or **Void / Cancel**.</t>
-        </is>
-      </c>
-      <c r="K113" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">Approved</t>
-        </is>
-      </c>
-      <c r="L113" t="inlineStr" s="2">
+      <c r="I114" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Atomic, Negative, Business-Rule</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Added 2026-10-01 for `PO-30` condition (5), which had no case. Admin only: the Portal needs no lock (`PO-25`, TC-AGENCY-081). TC-BR-101 is the contrast — same booking, lock taken, button shown. Not yet observed: run-008 did not record the button with the lock released. Never click **Reissue**, **Release PNR** or **Void / Cancel**. Status **Booked** in Booking Information **and** the status bar reading **"Ticketed Document"** are both required (`PO-30`).</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Pending</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">TC-BR-114</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Admin hides Reissue for an offline (imported) Branch booking</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Verify that the Admin Itinerary does not show Reissue on a Branch booking that was not made online (`PO-30` condition 4).</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">`{OFFLINE_REF}` — a BRN265 booking with Booking Type **Offline** (imported, not booked online), supplied by the user (§0.3). It is on a reissue-capable GDS (Sabre), its credential is in BRN265's Auto Reissue selection, Status **Booked**, status bar **"Ticketed Document"**, and it is not locked by another user. BRN265 has Auto Reissue on (Approved).</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">1. Open **Booking-Mid Office → Search Booking** (`/booking/search-booking`). | 2. Click the **Flight** tab. | 3. Enter Booking Reference `{OFFLINE_REF}` and click **Search**. | 4. Open the booking from the result row. | 5. Confirm Booking Information reads Booking Type **Offline** (or the imported equivalent) and Status **Booked**, and the status bar reads **"Ticketed Document"**. Record the exact Booking Type label. | 6. Click the lock icon on the **Created By** card and confirm it shows your name. | 7. Click **View Passenger Details**.</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">The **Reissue** button is not shown.</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">P2</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Atomic, Negative, Business-Rule</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Added 2026-10-01 for `PO-30` condition (4), which had no case. **The platform never books or imports** (`PO-19`): the user supplies `{OFFLINE_REF}`. Without one, record **Blocked — awaiting booking from the user**. If its credential or status differs from the preconditions, record what was seen and Blocked, not Failed. Never click **Reissue**, **Release PNR** or **Void / Cancel**.</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Pending</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Pending</t>
         </is>
